--- a/7_semestar/Poeni_7.XLSX
+++ b/7_semestar/Poeni_7.XLSX
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gitHub\Fakultetski_Materijal\7_semestar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159FA8BE-C610-4E49-A46D-9AB0B48A43E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796B0E3F-048D-4114-BBF3-F1F375305A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -75,10 +86,10 @@
     <t>Računarska Grafika</t>
   </si>
   <si>
-    <t>Projektovanje Računarskih Mreža</t>
-  </si>
-  <si>
     <t>Računarski Vid</t>
+  </si>
+  <si>
+    <t>Tehnologije za podrsku ucenju</t>
   </si>
 </sst>
 </file>
@@ -127,7 +138,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -152,8 +163,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -187,36 +204,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -321,52 +308,52 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -657,148 +644,186 @@
   </cols>
   <sheetData>
     <row r="11" spans="7:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="G11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="12" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10">
+        <v>2</v>
+      </c>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="10"/>
     </row>
     <row r="13" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
     </row>
     <row r="14" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
     </row>
     <row r="15" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
     </row>
     <row r="16" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
     </row>
     <row r="17" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="15"/>
     </row>
     <row r="18" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
     </row>
     <row r="19" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
     </row>
     <row r="20" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
     </row>
     <row r="21" spans="7:13" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+      <c r="H21" s="13">
+        <f xml:space="preserve"> H12 + H13 + H14 + H15 + H16 +H17+H18+H19+H20</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="13">
+        <f t="shared" ref="I21:M21" si="0" xml:space="preserve"> I12 + I13 + I14 + I15 + I16 +I17+I18+I19+I20</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K21" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="7:13" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="7"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="2"/>
+      <c r="H22" s="5">
+        <f>INT((H21 - 1) / 10) + 1</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" ref="I22:M22" si="1">INT((I21 - 1) / 10) + 1</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K22" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/7_semestar/Poeni_7.XLSX
+++ b/7_semestar/Poeni_7.XLSX
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gitHub\Fakultetski_Materijal\7_semestar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796B0E3F-048D-4114-BBF3-F1F375305A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026CDD00-1CF2-48A4-B2BD-DAD793D1DA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,7 +138,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -169,6 +169,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -306,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -332,12 +338,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -354,6 +354,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -640,10 +652,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="18.6640625" customWidth="1"/>
-    <col min="8" max="13" width="15.77734375" customWidth="1"/>
+    <col min="8" max="13" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="7:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="7:13" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G11" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,147 +678,163 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G12" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10">
-        <v>2</v>
-      </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="10"/>
-    </row>
-    <row r="13" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H12" s="15">
+        <v>20</v>
+      </c>
+      <c r="I12" s="16">
+        <v>20</v>
+      </c>
+      <c r="J12" s="16">
+        <v>10</v>
+      </c>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G13" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-    </row>
-    <row r="14" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H13" s="17">
+        <v>19.5</v>
+      </c>
+      <c r="I13" s="18">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G14" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-    </row>
-    <row r="15" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H14" s="17">
+        <v>19.5</v>
+      </c>
+      <c r="I14" s="18">
+        <v>18.670000000000002</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+    </row>
+    <row r="15" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-    </row>
-    <row r="16" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="9"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G16" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H16" s="9"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+    </row>
+    <row r="17" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="15"/>
-    </row>
-    <row r="18" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H17" s="14"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G18" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="14"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+    </row>
+    <row r="19" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G19" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-    </row>
-    <row r="20" spans="7:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H19" s="14"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+    </row>
+    <row r="20" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-    </row>
-    <row r="21" spans="7:13" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H20" s="17">
+        <v>7.5</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+    </row>
+    <row r="21" spans="7:13" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G21" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="13">
-        <f xml:space="preserve"> H12 + H13 + H14 + H15 + H16 +H17+H18+H19+H20</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="13">
+      <c r="H21" s="11">
+        <f>SUM(H12:H20)</f>
+        <v>66.5</v>
+      </c>
+      <c r="I21" s="11">
         <f t="shared" ref="I21:M21" si="0" xml:space="preserve"> I12 + I13 + I14 + I15 + I16 +I17+I18+I19+I20</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="13">
+        <v>56.52</v>
+      </c>
+      <c r="J21" s="11">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K21" s="13">
+        <v>10</v>
+      </c>
+      <c r="K21" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="7:13" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="7:13" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G22" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H22" s="5">
         <f>INT((H21 - 1) / 10) + 1</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" ref="I22:M22" si="1">INT((I21 - 1) / 10) + 1</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J22" s="5">
         <f t="shared" si="1"/>
@@ -822,7 +850,7 @@
       </c>
       <c r="M22" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/7_semestar/Poeni_7.XLSX
+++ b/7_semestar/Poeni_7.XLSX
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gitHub\Fakultetski_Materijal\7_semestar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Fakultetski_Materijal\7_semestar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026CDD00-1CF2-48A4-B2BD-DAD793D1DA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4573042-DD54-4679-8CAF-6F0DDCA8D8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -312,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -336,9 +336,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -649,13 +646,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="G11:M22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="18.6640625" customWidth="1"/>
-    <col min="8" max="13" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="13" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="7:13" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="7:13" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G11" s="1" t="s">
         <v>0</v>
       </c>
@@ -678,153 +675,153 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="7:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G12" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="14">
         <v>20</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="15">
         <v>20</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="15">
         <v>10</v>
       </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="16">
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="15">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="7:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G13" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="16">
         <v>19.5</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="17">
         <v>17.850000000000001</v>
       </c>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-    </row>
-    <row r="14" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" spans="7:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G14" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="16">
         <v>19.5</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="17">
         <v>18.670000000000002</v>
       </c>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-    </row>
-    <row r="15" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+    </row>
+    <row r="15" spans="7:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-    </row>
-    <row r="16" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="16"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" spans="7:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G16" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-    </row>
-    <row r="17" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H16" s="16"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+    </row>
+    <row r="17" spans="7:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="13"/>
-    </row>
-    <row r="18" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H17" s="13"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="12"/>
+    </row>
+    <row r="18" spans="7:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G18" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="14"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-    </row>
-    <row r="19" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="13"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+    </row>
+    <row r="19" spans="7:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G19" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="14"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-    </row>
-    <row r="20" spans="7:13" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H19" s="13"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+    </row>
+    <row r="20" spans="7:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="16">
         <v>7.5</v>
       </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-    </row>
-    <row r="21" spans="7:13" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I20" s="12"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+    </row>
+    <row r="21" spans="7:13" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G21" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="10">
         <f>SUM(H12:H20)</f>
         <v>66.5</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="10">
         <f t="shared" ref="I21:M21" si="0" xml:space="preserve"> I12 + I13 + I14 + I15 + I16 +I17+I18+I19+I20</f>
         <v>56.52</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="10">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L21" s="11">
+      <c r="L21" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M21" s="11">
+      <c r="M21" s="10">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="7:13" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="7:13" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G22" s="8" t="s">
         <v>11</v>
       </c>
